--- a/www/download/IND.abstract_labour.empe.s.mv.rpO2.xlsx
+++ b/www/download/IND.abstract_labour.empe.s.mv.rpO2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>21659.809</t>
+          <t>21659809032.2043</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>21661.706</t>
+          <t>21661706116.1805</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>23512.193</t>
+          <t>23512192768.7526</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23614.053</t>
+          <t>23614053471.7728</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>24944.607</t>
+          <t>24944607407.6095</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>24910.87</t>
+          <t>24910869999.2249</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>28581.17</t>
+          <t>28581170488.3728</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>25879.402</t>
+          <t>25879402288.7874</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>29201.948</t>
+          <t>29201948183.3771</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>46684.397</t>
+          <t>46684397123.162</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>35275.913</t>
+          <t>35275912997.7741</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>34030.086</t>
+          <t>34030086387.1539</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>30770.968</t>
+          <t>30770968059.1169</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>33373.296</t>
+          <t>33373295656.1317</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>35195.119</t>
+          <t>35195119383.2418</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11291.087</t>
+          <t>11291086512.9819</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11321.096</t>
+          <t>11321095799.4929</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11106.82</t>
+          <t>11106819669.8362</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>11242.423</t>
+          <t>11242422966.7255</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>12156.427</t>
+          <t>12156427497.2274</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>12910.225</t>
+          <t>12910224781.9165</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13110.594</t>
+          <t>13110594079.3261</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13655.15</t>
+          <t>13655149909.1003</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>14119.423</t>
+          <t>14119422574.1447</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>14529.787</t>
+          <t>14529786677.9273</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>13728.912</t>
+          <t>13728912276.4265</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>13493.643</t>
+          <t>13493643450.6496</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>13551.271</t>
+          <t>13551271051.0268</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>13816.535</t>
+          <t>13816534972.2439</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>13367.766</t>
+          <t>13367766339.7425</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20336.353</t>
+          <t>20336353292.1275</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20498.029</t>
+          <t>20498028759.5908</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>21029.865</t>
+          <t>21029864781.6991</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>21015.04</t>
+          <t>21015040073.4356</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>21764.807</t>
+          <t>21764807167.0252</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>22242.557</t>
+          <t>22242556781.5299</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>22370.699</t>
+          <t>22370699377.175</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>22185.713</t>
+          <t>22185713103.558</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>21982.728</t>
+          <t>21982727842.4757</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>22123.971</t>
+          <t>22123970786.1759</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>22656.223</t>
+          <t>22656223482.7146</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>23116.124</t>
+          <t>23116124137.9451</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>23728.509</t>
+          <t>23728509014.3337</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>24203.982</t>
+          <t>24203981854.6768</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>23776.63</t>
+          <t>23776630210.0671</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9147.748</t>
+          <t>9147748097.54196</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9565.603</t>
+          <t>9565603394.66537</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9483.489</t>
+          <t>9483489488.67567</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>8415.82</t>
+          <t>8415819565.6243</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8022.346</t>
+          <t>8022346256.71323</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7739.501</t>
+          <t>7739500840.15192</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8913.617</t>
+          <t>8913616931.51052</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8815.313</t>
+          <t>8815312524.52007</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>8406.174</t>
+          <t>8406174482.64817</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>8297.471</t>
+          <t>8297471066.15984</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>8001.593</t>
+          <t>8001592651.11045</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>7626.531</t>
+          <t>7626531030.85376</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>8259.292</t>
+          <t>8259291759.9885</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>10137.239</t>
+          <t>10137238761.0955</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>9721.443</t>
+          <t>9721443497.68812</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>776424.943</t>
+          <t>776424942710.667</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>747227.477</t>
+          <t>747227477290.262</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>747318.098</t>
+          <t>747318097662.155</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>732621.924</t>
+          <t>732621924167.388</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>748852.361</t>
+          <t>748852360508.389</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>672382.619</t>
+          <t>672382619326.985</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>663089.732</t>
+          <t>663089731923.17</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>671800.89</t>
+          <t>671800889828.283</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>628638.864</t>
+          <t>628638864307.615</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>646126.793</t>
+          <t>646126793476.04</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>649332.006</t>
+          <t>649332005860.839</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>676019.402</t>
+          <t>676019401565.162</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>740836.787</t>
+          <t>740836787398.288</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>774578.773</t>
+          <t>774578773076.183</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>807169.885</t>
+          <t>807169885410.541</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>66772.741</t>
+          <t>66772741070.9552</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>65488.882</t>
+          <t>65488882319.3572</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>61137.459</t>
+          <t>61137459452.3772</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>58965.107</t>
+          <t>58965106925.7631</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>63261.3</t>
+          <t>63261300044.2249</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>60292.23</t>
+          <t>60292229683.5288</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>64145.085</t>
+          <t>64145085221.6458</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>64254.994</t>
+          <t>64254993661.4251</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>64283.388</t>
+          <t>64283388285.599</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>67875.232</t>
+          <t>67875231862.5921</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>64472.074</t>
+          <t>64472074499.4515</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>69322.216</t>
+          <t>69322216363.1647</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>73245.966</t>
+          <t>73245966114.5455</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>75153.946</t>
+          <t>75153946309.8143</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>73697.743</t>
+          <t>73697742576.469</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2739016.305</t>
+          <t>2739016305466.46</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2807625.458</t>
+          <t>2807625457805.26</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2621023.398</t>
+          <t>2621023398408.73</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2493877.061</t>
+          <t>2493877061435.99</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2264588.286</t>
+          <t>2264588285619.46</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2373369.431</t>
+          <t>2373369431025.06</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2818388.63</t>
+          <t>2818388629942.08</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3103862.899</t>
+          <t>3103862898866.44</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3517992.439</t>
+          <t>3517992439067.94</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4061218.119</t>
+          <t>4061218119208.12</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>4385883.425</t>
+          <t>4385883424853.91</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4375218.148</t>
+          <t>4375218147799.91</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>4810376.994</t>
+          <t>4810376994052.82</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>5056270.271</t>
+          <t>5056270270902.14</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>5201748.001</t>
+          <t>5201748001103.75</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1502.35</t>
+          <t>1502350298.01866</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1456.363</t>
+          <t>1456363077.66808</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1458.468</t>
+          <t>1458468152.5686</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1437.1</t>
+          <t>1437100024.38513</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1413.85</t>
+          <t>1413850459.25908</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1408.541</t>
+          <t>1408541243.90918</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1503.04</t>
+          <t>1503040159.56097</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1606.128</t>
+          <t>1606127590.06637</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1902.436</t>
+          <t>1902435993.4233</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2063.599</t>
+          <t>2063598914.05356</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2161.748</t>
+          <t>2161747926.76914</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2398.483</t>
+          <t>2398482968.44396</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2391.134</t>
+          <t>2391134174.44464</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2888.32</t>
+          <t>2888319517.11536</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>3800.741</t>
+          <t>3800741129.69871</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13028.94</t>
+          <t>13028940099.4853</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>13106.997</t>
+          <t>13106997298.6239</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>13062.443</t>
+          <t>13062442761.339</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>13259.717</t>
+          <t>13259716551.7919</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>13237.922</t>
+          <t>13237921791.2094</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>13506.079</t>
+          <t>13506078876.5259</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>12561.898</t>
+          <t>12561897981.9356</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>12180.289</t>
+          <t>12180289210.9944</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>12563.456</t>
+          <t>12563455653.995</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>12597.239</t>
+          <t>12597239249.8264</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>12906.983</t>
+          <t>12906982990.7504</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>13275.868</t>
+          <t>13275868360.8551</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>13779.196</t>
+          <t>13779195611.9364</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>14612.196</t>
+          <t>14612196262.7781</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>15015.311</t>
+          <t>15015310789.8725</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>100379.878</t>
+          <t>100379877991.02</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>100180.921</t>
+          <t>100180920724.123</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>97510.408</t>
+          <t>97510407924.1113</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>98666.196</t>
+          <t>98666196436.9116</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>98143.717</t>
+          <t>98143717204.1581</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>97590.783</t>
+          <t>97590783419.4089</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>98172.016</t>
+          <t>98172015902.0671</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>97983.739</t>
+          <t>97983739269.334</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>96073.109</t>
+          <t>96073108606.517</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>99169.914</t>
+          <t>99169913925.5925</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>98195.722</t>
+          <t>98195721876.1549</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>98742.772</t>
+          <t>98742772342.1634</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>100842.371</t>
+          <t>100842370554.749</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>108265.945</t>
+          <t>108265945184.044</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>102226.466</t>
+          <t>102226465807.718</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6366.173</t>
+          <t>6366173355.16077</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6586.968</t>
+          <t>6586968044.45178</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7049.436</t>
+          <t>7049436036.98657</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>8206.644</t>
+          <t>8206644112.78081</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8693.476</t>
+          <t>8693476150.99804</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8948.9</t>
+          <t>8948900375.89216</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>9513.577</t>
+          <t>9513577428.87074</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>9692.561</t>
+          <t>9692560600.65442</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>9729.738</t>
+          <t>9729737527.56443</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>9721.681</t>
+          <t>9721680616.34719</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>10113.234</t>
+          <t>10113234210.1211</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>11030.481</t>
+          <t>11030480908.8319</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>11641.65</t>
+          <t>11641650061.9618</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>11348.79</t>
+          <t>11348789848.3873</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>11650.388</t>
+          <t>11650388297.2373</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>48266.631</t>
+          <t>48266630552.7277</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>47320.801</t>
+          <t>47320800634.7547</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>47281.679</t>
+          <t>47281679051.179</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>49001.923</t>
+          <t>49001922611.555</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>50608.691</t>
+          <t>50608691001.5012</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>52594.533</t>
+          <t>52594533470.1839</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>54122.381</t>
+          <t>54122380614.8208</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>57445.587</t>
+          <t>57445586721.7824</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>61574.415</t>
+          <t>61574415396.5121</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>63490.799</t>
+          <t>63490798804.8467</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>64924.313</t>
+          <t>64924313320.3242</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>66755.266</t>
+          <t>66755266211.4332</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>68101.645</t>
+          <t>68101645124.6501</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>71197.712</t>
+          <t>71197711986.1952</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>70265.847</t>
+          <t>70265847207.2307</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>10654.695</t>
+          <t>10654694881.9317</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10582.676</t>
+          <t>10582675915.0618</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18430.337</t>
+          <t>18430337402.6603</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>19548.337</t>
+          <t>19548336680.9985</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2084.56</t>
+          <t>2084559690.29115</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1964.15</t>
+          <t>1964149582.96943</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2966.838</t>
+          <t>2966837565.13008</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1995.069</t>
+          <t>1995069270.63942</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1836.995</t>
+          <t>1836994663.2494</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2229.898</t>
+          <t>2229897564.92767</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>3016.6</t>
+          <t>3016600249.88264</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2271.824</t>
+          <t>2271823985.39392</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2252.238</t>
+          <t>2252237985.36891</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2386.378</t>
+          <t>2386377694.37222</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1901.287</t>
+          <t>1901286897.48698</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7227.152</t>
+          <t>7227152371.4023</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7221.083</t>
+          <t>7221083440.39977</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7485.548</t>
+          <t>7485548189.51271</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7650.818</t>
+          <t>7650818445.135</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>7733.705</t>
+          <t>7733704720.94357</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7826.482</t>
+          <t>7826482031.80885</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7796.152</t>
+          <t>7796152067.07386</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>7565.416</t>
+          <t>7565415589.70168</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>7226.346</t>
+          <t>7226345974.46528</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>7330.1</t>
+          <t>7330100201.04219</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>7524.311</t>
+          <t>7524311320.64091</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>7673.806</t>
+          <t>7673806302.35284</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>7810.847</t>
+          <t>7810846695.85816</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>8247.854</t>
+          <t>8247854086.94774</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>7933.031</t>
+          <t>7933030975.73029</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>57914.808</t>
+          <t>57914807578.6457</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>58369.035</t>
+          <t>58369035146.9841</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>58805.176</t>
+          <t>58805176016.4786</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>63607.612</t>
+          <t>63607611938.6137</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>66335.937</t>
+          <t>66335936576.0391</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>65743.957</t>
+          <t>65743956637.0908</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>65367.274</t>
+          <t>65367273537.9871</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>63931.235</t>
+          <t>63931235311.9186</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>63098.189</t>
+          <t>63098188807.3458</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>62603.841</t>
+          <t>62603840883.4134</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>62772.234</t>
+          <t>62772233901.6289</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>63241.596</t>
+          <t>63241595579.0296</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>63447.488</t>
+          <t>63447488070.0761</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>66102.457</t>
+          <t>66102457094.678</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>65242.248</t>
+          <t>65242247584.8784</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>58642.666</t>
+          <t>58642665986.5646</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>63514.591</t>
+          <t>63514591348.8234</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>72643.74</t>
+          <t>72643740231.296</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>75261.571</t>
+          <t>75261570711.0046</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>73706.005</t>
+          <t>73706004789.8718</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>73516.585</t>
+          <t>73516585079.9033</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>72893.329</t>
+          <t>72893328570.2312</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>75062.6</t>
+          <t>75062599632.9462</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>74711.832</t>
+          <t>74711832182.7502</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>78157.826</t>
+          <t>78157826046.3048</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>80800.771</t>
+          <t>80800771188.7679</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>78628.394</t>
+          <t>78628393921.319</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>75815.337</t>
+          <t>75815336866.0359</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>71069.278</t>
+          <t>71069278310.7678</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>63516.34</t>
+          <t>63516340020.168</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>13520.954</t>
+          <t>13520953807.978</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13456.606</t>
+          <t>13456606394.5888</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>15269.2</t>
+          <t>15269200444.0178</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>15742.551</t>
+          <t>15742550919.895</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>15330.165</t>
+          <t>15330164643.4927</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>14833.996</t>
+          <t>14833996220.9253</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>13043.266</t>
+          <t>13043265848.5451</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>12856.996</t>
+          <t>12856996452.0579</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>12655.497</t>
+          <t>12655496733.6787</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>15395.259</t>
+          <t>15395259027.9691</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>12406.227</t>
+          <t>12406226779.6471</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>14114.585</t>
+          <t>14114585444.5893</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>14290.356</t>
+          <t>14290356382.9196</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>16474.463</t>
+          <t>16474463033.1927</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>17741.56</t>
+          <t>17741560026.8848</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>12745.035</t>
+          <t>12745034759.1789</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>12379.29</t>
+          <t>12379289943.7134</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>14396.82</t>
+          <t>14396820199.8513</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>15122.891</t>
+          <t>15122890787.1642</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>14295.418</t>
+          <t>14295418094.6636</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>16078.832</t>
+          <t>16078831885.3231</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>14963.864</t>
+          <t>14963864184.3045</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>17940.57</t>
+          <t>17940569618.8806</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>16760.537</t>
+          <t>16760537383.9542</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>16995.686</t>
+          <t>16995685653.018</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>16651.055</t>
+          <t>16651055324.339</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>18084.884</t>
+          <t>18084883959.5291</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>18997.403</t>
+          <t>18997402686.1033</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>21053.317</t>
+          <t>21053317228.103</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>21359.815</t>
+          <t>21359815197.5699</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>408192.496</t>
+          <t>408192495830.386</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>445101.632</t>
+          <t>445101632482.837</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>429550.943</t>
+          <t>429550942890.504</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>416003.067</t>
+          <t>416003067089.448</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>323376.194</t>
+          <t>323376194236.453</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>248525.374</t>
+          <t>248525373836.381</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>226130.307</t>
+          <t>226130307339.696</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>253447.461</t>
+          <t>253447460910.781</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>248049.63</t>
+          <t>248049629614.775</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>270084.685</t>
+          <t>270084685426.771</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>252482.502</t>
+          <t>252482501622.283</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>244635.664</t>
+          <t>244635664071.663</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>254016.81</t>
+          <t>254016809550.981</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>245243.31</t>
+          <t>245243309752.107</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>242465.21</t>
+          <t>242465210461.217</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2446008.567</t>
+          <t>2446008566998.67</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2203920.241</t>
+          <t>2203920240603.71</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2089514.485</t>
+          <t>2089514484573.32</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1811003.708</t>
+          <t>1811003707526.54</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1652682.515</t>
+          <t>1652682514658.23</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2194780.14</t>
+          <t>2194780140002.99</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2753869.057</t>
+          <t>2753869057278.55</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>3273603.713</t>
+          <t>3273603712904.26</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>3875012.297</t>
+          <t>3875012296628.37</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>4571139.566</t>
+          <t>4571139565521.3</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>4920482.177</t>
+          <t>4920482176610.61</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>4966195.46</t>
+          <t>4966195459526.66</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>4991850.117</t>
+          <t>4991850117319.73</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>5261183.76</t>
+          <t>5261183759996.08</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>5568684.316</t>
+          <t>5568684315920.31</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>8550.898</t>
+          <t>8550898110.10567</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8937.467</t>
+          <t>8937467253.45856</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>5707.823</t>
+          <t>5707822619.32336</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>5737.294</t>
+          <t>5737293943.36017</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>6263.888</t>
+          <t>6263887989.17367</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6912.402</t>
+          <t>6912402488.7068</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>7196.365</t>
+          <t>7196365021.61537</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>6935.815</t>
+          <t>6935815023.78472</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>6415.481</t>
+          <t>6415480766.4743</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>5700.85</t>
+          <t>5700850254.58018</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>6130.233</t>
+          <t>6130233044.84375</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>6385.395</t>
+          <t>6385394876.91745</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>6309.355</t>
+          <t>6309354956.59929</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>7120.348</t>
+          <t>7120348136.40928</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>5970.48</t>
+          <t>5970480334.0377</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>93141.035</t>
+          <t>93141034920.8647</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>100651.716</t>
+          <t>100651715646.463</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>100646.409</t>
+          <t>100646409490.213</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>100847.272</t>
+          <t>100847272059.766</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>102587.261</t>
+          <t>102587261329.856</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>108875.352</t>
+          <t>108875352093.602</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>106665.2</t>
+          <t>106665199582.797</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>112014.544</t>
+          <t>112014544059.051</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>128722.058</t>
+          <t>128722058220.422</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>120151.111</t>
+          <t>120151111424.145</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>119429.531</t>
+          <t>119429531140.44</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>120907.311</t>
+          <t>120907310918.804</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>115571.8</t>
+          <t>115571800114.507</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>112436.574</t>
+          <t>112436574237.623</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>108190.917</t>
+          <t>108190917247.705</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>323515.75</t>
+          <t>323515750265.628</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>289615.529</t>
+          <t>289615529129.559</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>317530.51</t>
+          <t>317530509580.758</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>324936.383</t>
+          <t>324936382531.141</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>292805.013</t>
+          <t>292805013277.706</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>340983.327</t>
+          <t>340983326521.757</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>329801.709</t>
+          <t>329801708624.655</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>306875.155</t>
+          <t>306875154863.086</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>303087.876</t>
+          <t>303087875838.832</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>308137.407</t>
+          <t>308137406604.413</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>314426.758</t>
+          <t>314426758147.864</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>323650.569</t>
+          <t>323650568843.841</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>327625.183</t>
+          <t>327625182567.348</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>319035.078</t>
+          <t>319035077537.594</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>294065.157</t>
+          <t>294065157457.993</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>85307.937</t>
+          <t>85307936783.2508</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>91473.859</t>
+          <t>91473859070.5107</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>93489.274</t>
+          <t>93489273724.437</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>90192.061</t>
+          <t>90192060930.8641</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>76516.482</t>
+          <t>76516481844.878</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>78116.229</t>
+          <t>78116228995.4659</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>80029.797</t>
+          <t>80029796819.1537</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>91803.848</t>
+          <t>91803847693.7433</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>93821.826</t>
+          <t>93821825739.6137</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>105394.826</t>
+          <t>105394826424.944</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>109225.463</t>
+          <t>109225463382.152</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>114728.903</t>
+          <t>114728902769.667</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>115367.129</t>
+          <t>115367129358.426</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>114138.263</t>
+          <t>114138263338.468</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>116171.426</t>
+          <t>116171425721.02</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>4246.387</t>
+          <t>4246386624.9874</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3829.263</t>
+          <t>3829262740.14418</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3629.61</t>
+          <t>3629609786.889</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4314.964</t>
+          <t>4314964173.69366</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4539.236</t>
+          <t>4539236065.83914</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4053.241</t>
+          <t>4053240684.79817</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3312.579</t>
+          <t>3312578976.68163</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>3661.625</t>
+          <t>3661625278.51256</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>3985.398</t>
+          <t>3985398196.18955</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>3555.36</t>
+          <t>3555359871.33692</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>4122.737</t>
+          <t>4122736535.24004</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>4793.387</t>
+          <t>4793387152.59972</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>4391.114</t>
+          <t>4391113677.20113</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>4412.322</t>
+          <t>4412322209.06167</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>5939.526</t>
+          <t>5939526015.8896</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1398.457</t>
+          <t>1398456929.20883</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>802.598</t>
+          <t>802597746.602435</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>738.086</t>
+          <t>738085926.578399</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>785.849</t>
+          <t>785848808.187841</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>843.42</t>
+          <t>843420118.02106</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>794.484</t>
+          <t>794483953.195013</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>750.549</t>
+          <t>750548785.577015</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>791.49</t>
+          <t>791489514.702266</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>808.648</t>
+          <t>808648330.600595</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>875.633</t>
+          <t>875633422.006662</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>874.63</t>
+          <t>874629633.53714</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>911.023</t>
+          <t>911022787.949523</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>952.99</t>
+          <t>952989545.387997</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1034.146</t>
+          <t>1034146465.2671</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1014.574</t>
+          <t>1014574476.11623</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3089.774</t>
+          <t>3089774321.19879</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3180.975</t>
+          <t>3180974768.29926</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2587.155</t>
+          <t>2587155496.58273</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2866.597</t>
+          <t>2866596597.04824</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3073.14</t>
+          <t>3073140140.91549</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3019.731</t>
+          <t>3019730766.4059</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2587.879</t>
+          <t>2587879094.3836</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3021.587</t>
+          <t>3021587034.04747</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4287.152</t>
+          <t>4287152245.10916</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>13273.009</t>
+          <t>13273009443.4513</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>276713.414</t>
+          <t>276713413756.414</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>41519.912</t>
+          <t>41519911839.359</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>3008.04</t>
+          <t>3008039503.66353</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>3170.196</t>
+          <t>3170195610.24025</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2849.516</t>
+          <t>2849516059.41487</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>229985.811</t>
+          <t>229985811484.388</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>237015.235</t>
+          <t>237015234553.143</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>247138.893</t>
+          <t>247138893374.143</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>255461.94</t>
+          <t>255461940006.793</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>268970.629</t>
+          <t>268970628828.494</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>280493.479</t>
+          <t>280493478513.076</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>283042.972</t>
+          <t>283042972196.605</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>289184.558</t>
+          <t>289184558351.265</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>307228.41</t>
+          <t>307228409542.958</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>342679.824</t>
+          <t>342679823539.474</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>344155.926</t>
+          <t>344155926260.046</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>337740.969</t>
+          <t>337740968839.035</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>350307.328</t>
+          <t>350307327736.802</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>406911.536</t>
+          <t>406911535568.92</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>404955.957</t>
+          <t>404955956767.774</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2656.676</t>
+          <t>2656676445.43296</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2648.968</t>
+          <t>2648967558.25063</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3923.768</t>
+          <t>3923767729.86454</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2810.843</t>
+          <t>2810842910.67806</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2983.768</t>
+          <t>2983768291.74709</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3163.349</t>
+          <t>3163348977.99599</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2120.304</t>
+          <t>2120303841.61417</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2470.043</t>
+          <t>2470042815.30797</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2445.973</t>
+          <t>2445973000.90932</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2522.292</t>
+          <t>2522291824.13757</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>3434.689</t>
+          <t>3434688599.42251</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2809.79</t>
+          <t>2809789510.10373</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>3046.618</t>
+          <t>3046617711.77182</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>3906.063</t>
+          <t>3906062728.91035</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>3672.468</t>
+          <t>3672468218.63372</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>15126.712</t>
+          <t>15126712283.1977</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>14377.496</t>
+          <t>14377495768.1579</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>15597.104</t>
+          <t>15597103866.7487</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>15963.124</t>
+          <t>15963123526.853</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>16999.782</t>
+          <t>16999782398.7614</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>16712.648</t>
+          <t>16712648209.6402</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>17818.927</t>
+          <t>17818926618.4838</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>17925.713</t>
+          <t>17925713327.3065</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>17283.752</t>
+          <t>17283751684.8882</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>16817.205</t>
+          <t>16817205279.9938</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>16578.966</t>
+          <t>16578965781.7726</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>17417.083</t>
+          <t>17417082797.036</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>17955.955</t>
+          <t>17955954887.6376</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>18668.962</t>
+          <t>18668961922.9997</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>18339.726</t>
+          <t>18339726349.2081</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>33339.639</t>
+          <t>33339638561.1408</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>32550.739</t>
+          <t>32550738694.2834</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>34254.527</t>
+          <t>34254527127.8094</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>33157.286</t>
+          <t>33157285529.1603</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>34180.437</t>
+          <t>34180437376.3308</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>34652.879</t>
+          <t>34652879324.3303</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>43282.226</t>
+          <t>43282226029.6693</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>46378.585</t>
+          <t>46378585043.3547</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>47000.521</t>
+          <t>47000520722.0171</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>46906.126</t>
+          <t>46906125690.6607</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>53728.648</t>
+          <t>53728647979.9121</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>54281.226</t>
+          <t>54281226398.82</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>53041.541</t>
+          <t>53041540718.422</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>51279.641</t>
+          <t>51279641482.2003</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>42981.496</t>
+          <t>42981496471.9942</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>16429.06</t>
+          <t>16429060196.1518</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>16297.968</t>
+          <t>16297968368.2815</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>16494.009</t>
+          <t>16494008710.8196</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>16885.269</t>
+          <t>16885268985.1287</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>17414.655</t>
+          <t>17414654698.3607</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>17832.353</t>
+          <t>17832352996.4713</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>17476.355</t>
+          <t>17476354652.1315</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>17280.514</t>
+          <t>17280513707.8614</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>16785.329</t>
+          <t>16785328608.3189</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>17043.937</t>
+          <t>17043936866.4833</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>17113.625</t>
+          <t>17113625282.2562</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>16253.24</t>
+          <t>16253240148.2155</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>15600.535</t>
+          <t>15600535258.8914</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>15764.605</t>
+          <t>15764604847.2518</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>15564.865</t>
+          <t>15564864500.3311</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>69894.184</t>
+          <t>69894184307.7031</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>60869.272</t>
+          <t>60869271876.9152</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>60429.298</t>
+          <t>60429297667.9292</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>56443.68</t>
+          <t>56443680424.6249</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>62212.485</t>
+          <t>62212485026.2834</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>61933.109</t>
+          <t>61933108873.4856</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>68345.307</t>
+          <t>68345307011.1097</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>65719.95</t>
+          <t>65719949530.5589</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>64357.004</t>
+          <t>64357004388.9044</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>80405.928</t>
+          <t>80405928486.4615</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>66932.145</t>
+          <t>66932144968.5817</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>70708.174</t>
+          <t>70708173542.6098</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>23056.169</t>
+          <t>23056168598.9616</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>24481.952</t>
+          <t>24481952464.9665</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>26501.867</t>
+          <t>26501867389.5057</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>647357.771</t>
+          <t>647357770564.593</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>557425.899</t>
+          <t>557425899398.8</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>476189.951</t>
+          <t>476189950722.272</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>433354.534</t>
+          <t>433354533947.366</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>383950.435</t>
+          <t>383950434514.297</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>389027.607</t>
+          <t>389027606586.69</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>403088.901</t>
+          <t>403088901432.379</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>396637.178</t>
+          <t>396637177790.879</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>396706.855</t>
+          <t>396706855145.379</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>476484.009</t>
+          <t>476484009322.767</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>529900.908</t>
+          <t>529900908156.09</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>520431.246</t>
+          <t>520431246185.125</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>505139.219</t>
+          <t>505139219240.835</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>501667.954</t>
+          <t>501667953563.184</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>465631.748</t>
+          <t>465631747663.243</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>4932.32</t>
+          <t>4932320458.62747</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5357.663</t>
+          <t>5357662845.37769</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>5033.614</t>
+          <t>5033614272.07582</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>4590.171</t>
+          <t>4590170558.31335</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>4757.157</t>
+          <t>4757156616.15005</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4509.101</t>
+          <t>4509100534.91624</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4671.932</t>
+          <t>4671931643.7201</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>4760.223</t>
+          <t>4760223422.43886</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>4507.246</t>
+          <t>4507245881.98335</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>4704.043</t>
+          <t>4704043480.95848</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>5001.948</t>
+          <t>5001948363.81823</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>5176.284</t>
+          <t>5176283644.90506</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>5109.161</t>
+          <t>5109161179.67623</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>5784.257</t>
+          <t>5784257464.48807</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>6271.9</t>
+          <t>6271900129.9571</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1883.476</t>
+          <t>1883475837.65772</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1986.392</t>
+          <t>1986392388.94569</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1946.219</t>
+          <t>1946218733.01739</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1993.527</t>
+          <t>1993526977.56097</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1974.155</t>
+          <t>1974155178.75338</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1998.785</t>
+          <t>1998784702.75494</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2025.935</t>
+          <t>2025934617.13986</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2077.662</t>
+          <t>2077662480.63342</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2081.213</t>
+          <t>2081213192.11853</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2084.627</t>
+          <t>2084626789.72716</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2091.793</t>
+          <t>2091793424.05369</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2159.049</t>
+          <t>2159048550.23829</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2122.051</t>
+          <t>2122050839.75942</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2467.583</t>
+          <t>2467583133.00859</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2328.265</t>
+          <t>2328265156.16674</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>8901.363</t>
+          <t>8901362512.59136</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>9177.04</t>
+          <t>9177040074.49592</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>9007.129</t>
+          <t>9007128540.90429</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>9254.752</t>
+          <t>9254751724.46151</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>9684.217</t>
+          <t>9684217187.03629</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>10212.891</t>
+          <t>10212891029.1434</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10427.86</t>
+          <t>10427860021.4307</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>10381.982</t>
+          <t>10381982019.2324</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>10172.977</t>
+          <t>10172976768.5968</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>10256.931</t>
+          <t>10256930756.506</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>10132.503</t>
+          <t>10132503196.9945</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>10855.813</t>
+          <t>10855812843.4152</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>10952.774</t>
+          <t>10952773572.5305</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>11238.977</t>
+          <t>11238977126.2814</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>9939.793</t>
+          <t>9939793337.42222</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>70280.55</t>
+          <t>70280550477.8989</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>71813.573</t>
+          <t>71813572604.138</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>67813.147</t>
+          <t>67813146596.1074</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>67072.094</t>
+          <t>67072093515.0636</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>63406.159</t>
+          <t>63406158745.6691</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>94983.886</t>
+          <t>94983886254.3783</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>127654.75</t>
+          <t>127654750085.161</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>298011.246</t>
+          <t>298011246183.741</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>336902.283</t>
+          <t>336902282732.786</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>378282.231</t>
+          <t>378282231193.487</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>397376.206</t>
+          <t>397376205826.463</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>438496.68</t>
+          <t>438496679865.973</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>420805.035</t>
+          <t>420805034734.893</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>371782.394</t>
+          <t>371782393982.02</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>558360.137</t>
+          <t>558360137403.406</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>42410.134</t>
+          <t>42410133545.3304</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>39923.091</t>
+          <t>39923090738.434</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>42218.292</t>
+          <t>42218292148.5933</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>42722.579</t>
+          <t>42722578563.0212</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>41917.602</t>
+          <t>41917602213.1982</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>44965.055</t>
+          <t>44965054527.3485</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>45594.057</t>
+          <t>45594056527.6413</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>42848.577</t>
+          <t>42848576677.127</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>42491.105</t>
+          <t>42491105359.2768</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>46366.911</t>
+          <t>46366911291.5793</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>48338.843</t>
+          <t>48338843286.4434</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>53800.127</t>
+          <t>53800127019.0627</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>58725.56</t>
+          <t>58725560221.8966</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>62417.061</t>
+          <t>62417061407.8992</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>61514.22</t>
+          <t>61514219939.3571</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>466021.311</t>
+          <t>466021311166.752</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>498609.46</t>
+          <t>498609460262.813</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>500803.999</t>
+          <t>500803998641.881</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>492011.342</t>
+          <t>492011341738.107</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>569406.486</t>
+          <t>569406486383.787</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>585696.435</t>
+          <t>585696434985.56</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>613078.546</t>
+          <t>613078546157.406</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>622941.067</t>
+          <t>622941066644.557</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>667028.973</t>
+          <t>667028972736.861</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>590076.797</t>
+          <t>590076796768.343</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>607949.937</t>
+          <t>607949936871.591</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>622767.405</t>
+          <t>622767404631.359</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>587909.794</t>
+          <t>587909794443.49</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>583382.673</t>
+          <t>583382673272.519</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>549542.764</t>
+          <t>549542764146.177</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>133194000.654</t>
+          <t>133194000654146</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>122694666.713</t>
+          <t>122694666713368</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>124330009.919</t>
+          <t>124330009919118</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>132267325.772</t>
+          <t>132267325771937</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>146824326.339</t>
+          <t>146824326338943</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>170432333.504</t>
+          <t>170432333503721</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>176870114.752</t>
+          <t>176870114752224</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>169885784.414</t>
+          <t>169885784413828</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>183815956.573</t>
+          <t>183815956572696</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>169870536.578</t>
+          <t>169870536578383</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>174892744.964</t>
+          <t>174892744963539</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>167293822.224</t>
+          <t>167293822224243</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>142506901.952</t>
+          <t>142506901952339</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>126938547.78</t>
+          <t>126938547780316</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>112745189.397</t>
+          <t>112745189397121</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>142151569.231</t>
+          <t>142151569230637</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>131407796.371</t>
+          <t>131407796371395</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>132702258.74</t>
+          <t>132702258739981</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>140172990.892</t>
+          <t>140172990891831</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>154260045.036</t>
+          <t>154260045035686</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>178492435.63</t>
+          <t>178492435629842</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>185990589.426</t>
+          <t>185990589426406</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>180023271.499</t>
+          <t>180023271498555</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>195037896.092</t>
+          <t>195037896091709</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>182520091.499</t>
+          <t>182520091499154</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>188550191.891</t>
+          <t>188550191891121</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>180845491.042</t>
+          <t>180845491041725</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>156459905.68</t>
+          <t>156459905679743</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>141447256.188</t>
+          <t>141447256188342</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>127801475.351</t>
+          <t>127801475350744</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>abstract_labour.empe.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
